--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -28341,15 +28329,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="B1539" t="inlineStr"/>
+      <c r="B1539" t="n">
+        <v>-3</v>
+      </c>
       <c r="C1539" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1539" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1540">
@@ -28360,10 +28350,10 @@
       </c>
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28390,21 +28380,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Italy WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-01-04 to 2026-03-22 | Publication days: 902</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-01-04 to 2026-03-22 | Publication days: 903</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -28412,22 +28402,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1540"/>
+  <dimension ref="A1:E1541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26846,13 +26846,13 @@
         </is>
       </c>
       <c r="B1459" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C1459" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1459" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E1459" t="b">
         <v>1</v>
@@ -26868,10 +26868,10 @@
         <v>0</v>
       </c>
       <c r="C1460" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1460" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E1460" t="b">
         <v>1</v>
@@ -26887,10 +26887,10 @@
         <v>0</v>
       </c>
       <c r="C1461" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1461" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E1461" t="b">
         <v>1</v>
@@ -26904,10 +26904,10 @@
       </c>
       <c r="B1462" t="inlineStr"/>
       <c r="C1462" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1462" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E1462" t="b">
         <v>0</v>
@@ -26921,10 +26921,10 @@
       </c>
       <c r="B1463" t="inlineStr"/>
       <c r="C1463" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1463" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E1463" t="b">
         <v>0</v>
@@ -26940,10 +26940,10 @@
         <v>0</v>
       </c>
       <c r="C1464" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1464" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E1464" t="b">
         <v>1</v>
@@ -26959,10 +26959,10 @@
         <v>0</v>
       </c>
       <c r="C1465" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1465" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1465" t="b">
         <v>1</v>
@@ -26981,7 +26981,7 @@
         <v>0</v>
       </c>
       <c r="D1466" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E1466" t="b">
         <v>1</v>
@@ -27000,7 +27000,7 @@
         <v>0</v>
       </c>
       <c r="D1467" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E1467" t="b">
         <v>1</v>
@@ -27019,7 +27019,7 @@
         <v>0</v>
       </c>
       <c r="D1468" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E1468" t="b">
         <v>1</v>
@@ -27038,7 +27038,7 @@
         <v>0</v>
       </c>
       <c r="D1469" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E1469" t="b">
         <v>1</v>
@@ -27055,7 +27055,7 @@
         <v>0</v>
       </c>
       <c r="D1470" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E1470" t="b">
         <v>0</v>
@@ -27074,7 +27074,7 @@
         <v>0</v>
       </c>
       <c r="D1471" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E1471" t="b">
         <v>1</v>
@@ -27091,7 +27091,7 @@
         <v>0</v>
       </c>
       <c r="D1472" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E1472" t="b">
         <v>0</v>
@@ -27110,7 +27110,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1473" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1473" t="b">
         <v>1</v>
@@ -27129,7 +27129,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1474" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1474" t="b">
         <v>1</v>
@@ -27148,7 +27148,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1475" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1475" t="b">
         <v>1</v>
@@ -27165,7 +27165,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1476" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1476" t="b">
         <v>0</v>
@@ -27184,7 +27184,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1477" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1477" t="b">
         <v>1</v>
@@ -27203,7 +27203,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1478" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1478" t="b">
         <v>1</v>
@@ -27222,7 +27222,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1479" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1479" t="b">
         <v>1</v>
@@ -27239,7 +27239,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1480" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1480" t="b">
         <v>0</v>
@@ -27258,7 +27258,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1481" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1481" t="b">
         <v>1</v>
@@ -27277,7 +27277,7 @@
         <v>1</v>
       </c>
       <c r="D1482" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1482" t="b">
         <v>1</v>
@@ -27294,7 +27294,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="D1483" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1483" t="b">
         <v>0</v>
@@ -27311,7 +27311,7 @@
         <v>1.857142857142857</v>
       </c>
       <c r="D1484" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1484" t="b">
         <v>0</v>
@@ -27330,7 +27330,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="D1485" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1485" t="b">
         <v>1</v>
@@ -27349,7 +27349,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1486" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1486" t="b">
         <v>1</v>
@@ -27368,7 +27368,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1487" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27387,7 +27387,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1488" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -28356,6 +28356,23 @@
         <v>-0.3666666666666666</v>
       </c>
       <c r="E1540" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr"/>
+      <c r="C1541" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D1541" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E1541" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28389,7 +28406,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-03-22 | Publication days: 903</t>
+          <t>Coverage: 2022-01-04 to 2026-03-23 | Publication days: 903</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1541"/>
+  <dimension ref="A1:E1542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28373,6 +28373,23 @@
         <v>-0.4666666666666667</v>
       </c>
       <c r="E1541" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr"/>
+      <c r="C1542" t="n">
+        <v>-2.142857142857143</v>
+      </c>
+      <c r="D1542" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E1542" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28406,7 +28423,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-03-23 | Publication days: 903</t>
+          <t>Coverage: 2022-01-04 to 2026-03-24 | Publication days: 903</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1542"/>
+  <dimension ref="A1:E1543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28390,6 +28390,23 @@
         <v>-0.6333333333333333</v>
       </c>
       <c r="E1542" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr"/>
+      <c r="C1543" t="n">
+        <v>-2.142857142857143</v>
+      </c>
+      <c r="D1543" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E1543" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28423,7 +28440,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-03-24 | Publication days: 903</t>
+          <t>Coverage: 2022-01-04 to 2026-03-25 | Publication days: 903</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -28312,7 +28312,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="B1538" t="inlineStr"/>
+      <c r="B1538" t="n">
+        <v>0</v>
+      </c>
       <c r="C1538" t="n">
         <v>-0.1428571428571428</v>
       </c>
@@ -28320,7 +28322,7 @@
         <v>-0.1666666666666667</v>
       </c>
       <c r="E1538" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1539">
@@ -28382,15 +28384,17 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="B1542" t="inlineStr"/>
+      <c r="B1542" t="n">
+        <v>0</v>
+      </c>
       <c r="C1542" t="n">
-        <v>-2.142857142857143</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1542" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1543">
@@ -28399,15 +28403,17 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="B1543" t="inlineStr"/>
+      <c r="B1543" t="n">
+        <v>0</v>
+      </c>
       <c r="C1543" t="n">
-        <v>-2.142857142857143</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1543" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -28440,7 +28446,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-03-25 | Publication days: 903</t>
+          <t>Coverage: 2022-01-04 to 2026-03-25 | Publication days: 906</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -28437,21 +28449,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Italy WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2022-01-04 to 2026-03-25 | Publication days: 906</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -28459,22 +28471,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1543"/>
+  <dimension ref="A1:E1544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -27283,13 +27271,13 @@
         </is>
       </c>
       <c r="B1482" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="C1482" t="n">
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1482" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1482" t="b">
         <v>1</v>
@@ -27303,10 +27291,10 @@
       </c>
       <c r="B1483" t="inlineStr"/>
       <c r="C1483" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D1483" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1483" t="b">
         <v>0</v>
@@ -27320,10 +27308,10 @@
       </c>
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="n">
-        <v>1.857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1484" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1484" t="b">
         <v>0</v>
@@ -27339,10 +27327,10 @@
         <v>-3</v>
       </c>
       <c r="C1485" t="n">
-        <v>1.428571428571429</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1485" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1485" t="b">
         <v>1</v>
@@ -27358,10 +27346,10 @@
         <v>0</v>
       </c>
       <c r="C1486" t="n">
-        <v>1.142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D1486" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1486" t="b">
         <v>1</v>
@@ -27377,10 +27365,10 @@
         <v>0</v>
       </c>
       <c r="C1487" t="n">
-        <v>0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1487" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27396,10 +27384,10 @@
         <v>0</v>
       </c>
       <c r="C1488" t="n">
-        <v>0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1488" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -27415,10 +27403,10 @@
         <v>0</v>
       </c>
       <c r="C1489" t="n">
-        <v>0.4285714285714285</v>
+        <v>-1</v>
       </c>
       <c r="D1489" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1489" t="b">
         <v>1</v>
@@ -27432,10 +27420,10 @@
       </c>
       <c r="B1490" t="inlineStr"/>
       <c r="C1490" t="n">
-        <v>0</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1490" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1490" t="b">
         <v>0</v>
@@ -27454,7 +27442,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1491" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1491" t="b">
         <v>1</v>
@@ -27471,7 +27459,7 @@
         <v>0</v>
       </c>
       <c r="D1492" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1492" t="b">
         <v>0</v>
@@ -27490,7 +27478,7 @@
         <v>0</v>
       </c>
       <c r="D1493" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1493" t="b">
         <v>1</v>
@@ -27509,7 +27497,7 @@
         <v>0</v>
       </c>
       <c r="D1494" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1494" t="b">
         <v>1</v>
@@ -27528,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="D1495" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1495" t="b">
         <v>1</v>
@@ -27547,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="D1496" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1496" t="b">
         <v>1</v>
@@ -27564,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="D1497" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1497" t="b">
         <v>0</v>
@@ -27581,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="D1498" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1498" t="b">
         <v>0</v>
@@ -27600,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="D1499" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1499" t="b">
         <v>1</v>
@@ -27619,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="D1500" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1500" t="b">
         <v>1</v>
@@ -27638,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="D1501" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1501" t="b">
         <v>1</v>
@@ -27657,7 +27645,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1502" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27676,7 +27664,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1503" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27695,7 +27683,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1504" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27712,7 +27700,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1505" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27731,7 +27719,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1506" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27750,7 +27738,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1507" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27769,7 +27757,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1508" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27788,7 +27776,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1509" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27807,7 +27795,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1510" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27826,7 +27814,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1511" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27839,13 +27827,13 @@
         </is>
       </c>
       <c r="B1512" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1512" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1512" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27861,10 +27849,10 @@
         <v>-2</v>
       </c>
       <c r="C1513" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.1</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27880,10 +27868,10 @@
         <v>0</v>
       </c>
       <c r="C1514" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1514" t="b">
         <v>1</v>
@@ -27897,10 +27885,10 @@
       </c>
       <c r="B1515" t="inlineStr"/>
       <c r="C1515" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.1</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27916,10 +27904,10 @@
         <v>0</v>
       </c>
       <c r="C1516" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.1</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27935,10 +27923,10 @@
         <v>-2</v>
       </c>
       <c r="C1517" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27952,10 +27940,10 @@
       </c>
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27974,7 +27962,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27993,7 +27981,7 @@
         <v>-1</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -28012,7 +28000,7 @@
         <v>-1</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28031,7 +28019,7 @@
         <v>-1</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28050,7 +28038,7 @@
         <v>-1</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28069,7 +28057,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28088,7 +28076,7 @@
         <v>0</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28107,7 +28095,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28126,7 +28114,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28145,7 +28133,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28162,7 +28150,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28181,7 +28169,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28200,7 +28188,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28217,7 +28205,7 @@
         <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28236,7 +28224,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28255,7 +28243,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28274,7 +28262,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28293,7 +28281,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28306,13 +28294,13 @@
         </is>
       </c>
       <c r="B1537" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1537" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28328,10 +28316,10 @@
         <v>0</v>
       </c>
       <c r="C1538" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28347,10 +28335,10 @@
         <v>-3</v>
       </c>
       <c r="C1539" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28364,10 +28352,10 @@
       </c>
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28381,10 +28369,10 @@
       </c>
       <c r="B1541" t="inlineStr"/>
       <c r="C1541" t="n">
-        <v>-1.714285714285714</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28400,10 +28388,10 @@
         <v>0</v>
       </c>
       <c r="C1542" t="n">
-        <v>-1.714285714285714</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28419,13 +28407,30 @@
         <v>0</v>
       </c>
       <c r="C1543" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D1543" t="n">
+        <v>-0.3666666666666666</v>
+      </c>
+      <c r="E1543" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr"/>
+      <c r="C1544" t="n">
         <v>-1.285714285714286</v>
       </c>
-      <c r="D1543" t="n">
-        <v>-0.4666666666666667</v>
-      </c>
-      <c r="E1543" t="b">
-        <v>1</v>
+      <c r="D1544" t="n">
+        <v>-0.3666666666666666</v>
+      </c>
+      <c r="E1544" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -28449,21 +28454,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Italy WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-01-04 to 2026-03-25 | Publication days: 906</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-01-04 to 2026-03-26 | Publication days: 906</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -28471,22 +28476,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -28454,21 +28466,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Italy WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2022-01-04 to 2026-03-26 | Publication days: 906</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -28476,22 +28488,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -27283,13 +27271,13 @@
         </is>
       </c>
       <c r="B1482" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="C1482" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1482" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1482" t="b">
         <v>1</v>
@@ -27303,10 +27291,10 @@
       </c>
       <c r="B1483" t="inlineStr"/>
       <c r="C1483" t="n">
-        <v>0</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1483" t="n">
-        <v>-0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1483" t="b">
         <v>0</v>
@@ -27320,10 +27308,10 @@
       </c>
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="n">
-        <v>-0.2857142857142857</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1484" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1484" t="b">
         <v>0</v>
@@ -27339,10 +27327,10 @@
         <v>-3</v>
       </c>
       <c r="C1485" t="n">
-        <v>-0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="D1485" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1485" t="b">
         <v>1</v>
@@ -27358,10 +27346,10 @@
         <v>0</v>
       </c>
       <c r="C1486" t="n">
-        <v>-1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D1486" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1486" t="b">
         <v>1</v>
@@ -27377,10 +27365,10 @@
         <v>0</v>
       </c>
       <c r="C1487" t="n">
-        <v>-1.285714285714286</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1487" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27396,10 +27384,10 @@
         <v>0</v>
       </c>
       <c r="C1488" t="n">
-        <v>-1.285714285714286</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1488" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -27415,10 +27403,10 @@
         <v>0</v>
       </c>
       <c r="C1489" t="n">
-        <v>-1</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1489" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1489" t="b">
         <v>1</v>
@@ -27432,10 +27420,10 @@
       </c>
       <c r="B1490" t="inlineStr"/>
       <c r="C1490" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1490" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1490" t="b">
         <v>0</v>
@@ -27454,7 +27442,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1491" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1491" t="b">
         <v>1</v>
@@ -27471,7 +27459,7 @@
         <v>0</v>
       </c>
       <c r="D1492" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1492" t="b">
         <v>0</v>
@@ -27490,7 +27478,7 @@
         <v>0</v>
       </c>
       <c r="D1493" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1493" t="b">
         <v>1</v>
@@ -27509,7 +27497,7 @@
         <v>0</v>
       </c>
       <c r="D1494" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1494" t="b">
         <v>1</v>
@@ -27528,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="D1495" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1495" t="b">
         <v>1</v>
@@ -27547,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="D1496" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1496" t="b">
         <v>1</v>
@@ -27564,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="D1497" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1497" t="b">
         <v>0</v>
@@ -27581,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="D1498" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1498" t="b">
         <v>0</v>
@@ -27600,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="D1499" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1499" t="b">
         <v>1</v>
@@ -27619,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="D1500" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1500" t="b">
         <v>1</v>
@@ -27638,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="D1501" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1501" t="b">
         <v>1</v>
@@ -27657,7 +27645,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1502" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27676,7 +27664,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1503" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27695,7 +27683,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1504" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27712,7 +27700,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1505" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27731,7 +27719,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1506" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27744,13 +27732,13 @@
         </is>
       </c>
       <c r="B1507" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C1507" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="D1507" t="n">
-        <v>-0.2</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27766,10 +27754,10 @@
         <v>-2</v>
       </c>
       <c r="C1508" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1508" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27785,10 +27773,10 @@
         <v>0</v>
       </c>
       <c r="C1509" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1509" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27804,10 +27792,10 @@
         <v>0</v>
       </c>
       <c r="C1510" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1510" t="n">
-        <v>-0.4</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27823,10 +27811,10 @@
         <v>0</v>
       </c>
       <c r="C1511" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1511" t="n">
-        <v>-0.4</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27839,13 +27827,13 @@
         </is>
       </c>
       <c r="B1512" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1512" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1512" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27861,10 +27849,10 @@
         <v>-2</v>
       </c>
       <c r="C1513" t="n">
-        <v>-1</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27880,10 +27868,10 @@
         <v>0</v>
       </c>
       <c r="C1514" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1514" t="b">
         <v>1</v>
@@ -27897,10 +27885,10 @@
       </c>
       <c r="B1515" t="inlineStr"/>
       <c r="C1515" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27916,10 +27904,10 @@
         <v>0</v>
       </c>
       <c r="C1516" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27935,10 +27923,10 @@
         <v>-2</v>
       </c>
       <c r="C1517" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27952,10 +27940,10 @@
       </c>
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27974,7 +27962,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27993,7 +27981,7 @@
         <v>-1</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -28012,7 +28000,7 @@
         <v>-1</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28031,7 +28019,7 @@
         <v>-1</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28050,7 +28038,7 @@
         <v>-1</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28069,7 +28057,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28088,7 +28076,7 @@
         <v>0</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28107,7 +28095,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28126,7 +28114,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28139,13 +28127,13 @@
         </is>
       </c>
       <c r="B1528" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1528" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.3</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28159,10 +28147,10 @@
       </c>
       <c r="B1529" t="inlineStr"/>
       <c r="C1529" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.3</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28178,10 +28166,10 @@
         <v>0</v>
       </c>
       <c r="C1530" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.3</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28197,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="C1531" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.3</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28214,10 +28202,10 @@
       </c>
       <c r="B1532" t="inlineStr"/>
       <c r="C1532" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28233,10 +28221,10 @@
         <v>2</v>
       </c>
       <c r="C1533" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.3</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28252,10 +28240,10 @@
         <v>0</v>
       </c>
       <c r="C1534" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.3</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28271,10 +28259,10 @@
         <v>0</v>
       </c>
       <c r="C1535" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.3</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28293,7 +28281,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.4</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28306,13 +28294,13 @@
         </is>
       </c>
       <c r="B1537" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C1537" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.2</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28328,10 +28316,10 @@
         <v>0</v>
       </c>
       <c r="C1538" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28347,10 +28335,10 @@
         <v>-3</v>
       </c>
       <c r="C1539" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28364,10 +28352,10 @@
       </c>
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28381,10 +28369,10 @@
       </c>
       <c r="B1541" t="inlineStr"/>
       <c r="C1541" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28400,10 +28388,10 @@
         <v>0</v>
       </c>
       <c r="C1542" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28419,10 +28407,10 @@
         <v>0</v>
       </c>
       <c r="C1543" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.6</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28439,7 +28427,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.6</v>
       </c>
       <c r="E1544" t="b">
         <v>0</v>
@@ -28466,21 +28454,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Italy WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2022-01-04 to 2026-03-26 | Publication days: 906</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -28488,22 +28476,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1544"/>
+  <dimension ref="A1:E1545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -27228,13 +27216,13 @@
         </is>
       </c>
       <c r="B1479" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1479" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1479" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1479" t="b">
         <v>1</v>
@@ -27248,10 +27236,10 @@
       </c>
       <c r="B1480" t="inlineStr"/>
       <c r="C1480" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1480" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1480" t="b">
         <v>0</v>
@@ -27267,10 +27255,10 @@
         <v>0</v>
       </c>
       <c r="C1481" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1481" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1481" t="b">
         <v>1</v>
@@ -27286,10 +27274,10 @@
         <v>2</v>
       </c>
       <c r="C1482" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1482" t="n">
-        <v>0.1</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1482" t="b">
         <v>1</v>
@@ -27303,10 +27291,10 @@
       </c>
       <c r="B1483" t="inlineStr"/>
       <c r="C1483" t="n">
-        <v>1.142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1483" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1483" t="b">
         <v>0</v>
@@ -27320,10 +27308,10 @@
       </c>
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="n">
-        <v>1.428571428571429</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1484" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1484" t="b">
         <v>0</v>
@@ -27336,13 +27324,13 @@
         </is>
       </c>
       <c r="B1485" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C1485" t="n">
-        <v>1</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1485" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1485" t="b">
         <v>1</v>
@@ -27358,10 +27346,10 @@
         <v>0</v>
       </c>
       <c r="C1486" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1486" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1486" t="b">
         <v>1</v>
@@ -27377,10 +27365,10 @@
         <v>0</v>
       </c>
       <c r="C1487" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1487" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27396,10 +27384,10 @@
         <v>0</v>
       </c>
       <c r="C1488" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1488" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -27415,10 +27403,10 @@
         <v>0</v>
       </c>
       <c r="C1489" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1489" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1489" t="b">
         <v>1</v>
@@ -27432,10 +27420,10 @@
       </c>
       <c r="B1490" t="inlineStr"/>
       <c r="C1490" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="D1490" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1490" t="b">
         <v>0</v>
@@ -27451,10 +27439,10 @@
         <v>0</v>
       </c>
       <c r="C1491" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1491" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1491" t="b">
         <v>1</v>
@@ -27471,7 +27459,7 @@
         <v>0</v>
       </c>
       <c r="D1492" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1492" t="b">
         <v>0</v>
@@ -27490,7 +27478,7 @@
         <v>0</v>
       </c>
       <c r="D1493" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1493" t="b">
         <v>1</v>
@@ -27509,7 +27497,7 @@
         <v>0</v>
       </c>
       <c r="D1494" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1494" t="b">
         <v>1</v>
@@ -27528,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="D1495" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1495" t="b">
         <v>1</v>
@@ -27547,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="D1496" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1496" t="b">
         <v>1</v>
@@ -27564,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="D1497" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1497" t="b">
         <v>0</v>
@@ -27581,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="D1498" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1498" t="b">
         <v>0</v>
@@ -27600,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="D1499" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1499" t="b">
         <v>1</v>
@@ -27619,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="D1500" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1500" t="b">
         <v>1</v>
@@ -27638,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="D1501" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1501" t="b">
         <v>1</v>
@@ -27651,13 +27639,13 @@
         </is>
       </c>
       <c r="B1502" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1502" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1502" t="n">
-        <v>0.2</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27673,10 +27661,10 @@
         <v>0</v>
       </c>
       <c r="C1503" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1503" t="n">
-        <v>0.3</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27692,10 +27680,10 @@
         <v>0</v>
       </c>
       <c r="C1504" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1504" t="n">
-        <v>0.3</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27709,10 +27697,10 @@
       </c>
       <c r="B1505" t="inlineStr"/>
       <c r="C1505" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1505" t="n">
-        <v>0.3</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27728,10 +27716,10 @@
         <v>0</v>
       </c>
       <c r="C1506" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1506" t="n">
-        <v>0.3</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27747,10 +27735,10 @@
         <v>-2</v>
       </c>
       <c r="C1507" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1507" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27766,10 +27754,10 @@
         <v>-2</v>
       </c>
       <c r="C1508" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1508" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27788,7 +27776,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1509" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27807,7 +27795,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1510" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27826,7 +27814,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1511" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27845,7 +27833,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1512" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27864,7 +27852,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.1</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27883,7 +27871,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1514" t="b">
         <v>1</v>
@@ -27900,7 +27888,7 @@
         <v>0</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27919,7 +27907,7 @@
         <v>0</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27938,7 +27926,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27955,7 +27943,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27974,7 +27962,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27993,7 +27981,7 @@
         <v>-1</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -28012,7 +28000,7 @@
         <v>-1</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28031,7 +28019,7 @@
         <v>-1</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28050,7 +28038,7 @@
         <v>-1</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28069,7 +28057,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28088,7 +28076,7 @@
         <v>0</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28107,7 +28095,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28126,7 +28114,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28145,7 +28133,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28162,7 +28150,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28181,7 +28169,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28200,7 +28188,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28434,7 +28422,9 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="B1544" t="inlineStr"/>
+      <c r="B1544" t="n">
+        <v>0</v>
+      </c>
       <c r="C1544" t="n">
         <v>-1.285714285714286</v>
       </c>
@@ -28442,6 +28432,23 @@
         <v>-0.6</v>
       </c>
       <c r="E1544" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr"/>
+      <c r="C1545" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="D1545" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E1545" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28466,21 +28473,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Italy WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-01-04 to 2026-03-26 | Publication days: 906</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-01-04 to 2026-03-27 | Publication days: 907</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -28488,22 +28495,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -27216,13 +27216,13 @@
         </is>
       </c>
       <c r="B1479" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1479" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1479" t="n">
-        <v>-0.2</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1479" t="b">
         <v>1</v>
@@ -27236,10 +27236,10 @@
       </c>
       <c r="B1480" t="inlineStr"/>
       <c r="C1480" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1480" t="n">
-        <v>-0.2</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1480" t="b">
         <v>0</v>
@@ -27255,10 +27255,10 @@
         <v>0</v>
       </c>
       <c r="C1481" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1481" t="n">
-        <v>-0.2</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1481" t="b">
         <v>1</v>
@@ -27271,7 +27271,7 @@
         </is>
       </c>
       <c r="B1482" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="C1482" t="n">
         <v>0.2857142857142857</v>
@@ -27291,10 +27291,10 @@
       </c>
       <c r="B1483" t="inlineStr"/>
       <c r="C1483" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1483" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1483" t="b">
         <v>0</v>
@@ -27308,10 +27308,10 @@
       </c>
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1484" t="n">
-        <v>0.1</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1484" t="b">
         <v>0</v>
@@ -27324,13 +27324,13 @@
         </is>
       </c>
       <c r="B1485" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C1485" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1485" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1485" t="b">
         <v>1</v>
@@ -27346,10 +27346,10 @@
         <v>0</v>
       </c>
       <c r="C1486" t="n">
-        <v>0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D1486" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1486" t="b">
         <v>1</v>
@@ -27365,10 +27365,10 @@
         <v>0</v>
       </c>
       <c r="C1487" t="n">
-        <v>0.5714285714285714</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1487" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27384,10 +27384,10 @@
         <v>0</v>
       </c>
       <c r="C1488" t="n">
-        <v>0.5714285714285714</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1488" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -27403,10 +27403,10 @@
         <v>0</v>
       </c>
       <c r="C1489" t="n">
-        <v>0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D1489" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1489" t="b">
         <v>1</v>
@@ -27420,10 +27420,10 @@
       </c>
       <c r="B1490" t="inlineStr"/>
       <c r="C1490" t="n">
-        <v>0</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1490" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1490" t="b">
         <v>0</v>
@@ -27439,10 +27439,10 @@
         <v>0</v>
       </c>
       <c r="C1491" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1491" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1491" t="b">
         <v>1</v>
@@ -27459,7 +27459,7 @@
         <v>0</v>
       </c>
       <c r="D1492" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1492" t="b">
         <v>0</v>
@@ -27478,7 +27478,7 @@
         <v>0</v>
       </c>
       <c r="D1493" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1493" t="b">
         <v>1</v>
@@ -27497,7 +27497,7 @@
         <v>0</v>
       </c>
       <c r="D1494" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1494" t="b">
         <v>1</v>
@@ -27516,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="D1495" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1495" t="b">
         <v>1</v>
@@ -27535,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="D1496" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1496" t="b">
         <v>1</v>
@@ -27552,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="D1497" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1497" t="b">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="D1498" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1498" t="b">
         <v>0</v>
@@ -27588,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="D1499" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1499" t="b">
         <v>1</v>
@@ -27607,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="D1500" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1500" t="b">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="D1501" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1501" t="b">
         <v>1</v>
@@ -27639,13 +27639,13 @@
         </is>
       </c>
       <c r="B1502" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1502" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1502" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27661,10 +27661,10 @@
         <v>0</v>
       </c>
       <c r="C1503" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1503" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27680,10 +27680,10 @@
         <v>0</v>
       </c>
       <c r="C1504" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1504" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27697,10 +27697,10 @@
       </c>
       <c r="B1505" t="inlineStr"/>
       <c r="C1505" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1505" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27716,10 +27716,10 @@
         <v>0</v>
       </c>
       <c r="C1506" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1506" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27732,13 +27732,13 @@
         </is>
       </c>
       <c r="B1507" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C1507" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1507" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27754,10 +27754,10 @@
         <v>-2</v>
       </c>
       <c r="C1508" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1508" t="n">
-        <v>0</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27773,10 +27773,10 @@
         <v>0</v>
       </c>
       <c r="C1509" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1509" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27792,10 +27792,10 @@
         <v>0</v>
       </c>
       <c r="C1510" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1510" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27811,10 +27811,10 @@
         <v>0</v>
       </c>
       <c r="C1511" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1511" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27830,10 +27830,10 @@
         <v>2</v>
       </c>
       <c r="C1512" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1512" t="n">
-        <v>0</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27849,10 +27849,10 @@
         <v>-2</v>
       </c>
       <c r="C1513" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27888,7 +27888,7 @@
         <v>0</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27907,7 +27907,7 @@
         <v>0</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27926,7 +27926,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.2</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27943,7 +27943,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27962,7 +27962,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27981,7 +27981,7 @@
         <v>-1</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -28000,7 +28000,7 @@
         <v>-1</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28019,7 +28019,7 @@
         <v>-1</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28038,7 +28038,7 @@
         <v>-1</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28057,7 +28057,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28076,7 +28076,7 @@
         <v>0</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28095,7 +28095,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28114,7 +28114,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28133,7 +28133,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28150,7 +28150,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28169,7 +28169,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28188,7 +28188,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28205,7 +28205,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.4</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28224,7 +28224,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28243,7 +28243,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28262,7 +28262,7 @@
         <v>0</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28281,7 +28281,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28441,15 +28441,17 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B1545" t="inlineStr"/>
+      <c r="B1545" t="n">
+        <v>2</v>
+      </c>
       <c r="C1545" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.6</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1545" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -28482,7 +28484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-03-27 | Publication days: 907</t>
+          <t>Coverage: 2022-01-04 to 2026-03-27 | Publication days: 908</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1545"/>
+  <dimension ref="A1:E1546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27271,13 +27271,13 @@
         </is>
       </c>
       <c r="B1482" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="C1482" t="n">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="D1482" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1482" t="b">
         <v>1</v>
@@ -27291,10 +27291,10 @@
       </c>
       <c r="B1483" t="inlineStr"/>
       <c r="C1483" t="n">
-        <v>0</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1483" t="n">
-        <v>-0.1</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1483" t="b">
         <v>0</v>
@@ -27308,10 +27308,10 @@
       </c>
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="n">
-        <v>-0.2857142857142857</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D1484" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1484" t="b">
         <v>0</v>
@@ -27327,10 +27327,10 @@
         <v>-3</v>
       </c>
       <c r="C1485" t="n">
-        <v>-0.7142857142857143</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1485" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1485" t="b">
         <v>1</v>
@@ -27346,10 +27346,10 @@
         <v>0</v>
       </c>
       <c r="C1486" t="n">
-        <v>-1</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1486" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1486" t="b">
         <v>1</v>
@@ -27365,10 +27365,10 @@
         <v>0</v>
       </c>
       <c r="C1487" t="n">
-        <v>-1.285714285714286</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1487" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27384,10 +27384,10 @@
         <v>0</v>
       </c>
       <c r="C1488" t="n">
-        <v>-1.285714285714286</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1488" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -27403,10 +27403,10 @@
         <v>0</v>
       </c>
       <c r="C1489" t="n">
-        <v>-1</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1489" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1489" t="b">
         <v>1</v>
@@ -27420,10 +27420,10 @@
       </c>
       <c r="B1490" t="inlineStr"/>
       <c r="C1490" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1490" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1490" t="b">
         <v>0</v>
@@ -27442,7 +27442,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1491" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1491" t="b">
         <v>1</v>
@@ -27459,7 +27459,7 @@
         <v>0</v>
       </c>
       <c r="D1492" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1492" t="b">
         <v>0</v>
@@ -27478,7 +27478,7 @@
         <v>0</v>
       </c>
       <c r="D1493" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1493" t="b">
         <v>1</v>
@@ -27497,7 +27497,7 @@
         <v>0</v>
       </c>
       <c r="D1494" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1494" t="b">
         <v>1</v>
@@ -27516,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="D1495" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1495" t="b">
         <v>1</v>
@@ -27535,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="D1496" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1496" t="b">
         <v>1</v>
@@ -27552,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="D1497" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1497" t="b">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="D1498" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1498" t="b">
         <v>0</v>
@@ -27588,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="D1499" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1499" t="b">
         <v>1</v>
@@ -27607,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="D1500" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1500" t="b">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="D1501" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1501" t="b">
         <v>1</v>
@@ -27645,7 +27645,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1502" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27664,7 +27664,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1503" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27683,7 +27683,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1504" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27700,7 +27700,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1505" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27719,7 +27719,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1506" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27738,7 +27738,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1507" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27757,7 +27757,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1508" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27776,7 +27776,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1509" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27795,7 +27795,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1510" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27814,7 +27814,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1511" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27833,7 +27833,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1512" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27852,7 +27852,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.1</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -28452,6 +28452,23 @@
       </c>
       <c r="E1545" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr"/>
+      <c r="C1546" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D1546" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E1546" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -28484,7 +28501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-03-27 | Publication days: 908</t>
+          <t>Coverage: 2022-01-04 to 2026-03-28 | Publication days: 908</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1546"/>
+  <dimension ref="A1:E1547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28468,6 +28468,23 @@
         <v>-0.4666666666666667</v>
       </c>
       <c r="E1546" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr"/>
+      <c r="C1547" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="D1547" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="E1547" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28501,7 +28518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-03-28 | Publication days: 908</t>
+          <t>Coverage: 2022-01-04 to 2026-03-29 | Publication days: 908</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1547"/>
+  <dimension ref="A1:E1548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27920,13 +27920,13 @@
         </is>
       </c>
       <c r="B1517" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C1517" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27940,10 +27940,10 @@
       </c>
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27959,10 +27959,10 @@
         <v>-3</v>
       </c>
       <c r="C1519" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27978,10 +27978,10 @@
         <v>0</v>
       </c>
       <c r="C1520" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -27997,10 +27997,10 @@
         <v>0</v>
       </c>
       <c r="C1521" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28016,10 +28016,10 @@
         <v>0</v>
       </c>
       <c r="C1522" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28035,10 +28035,10 @@
         <v>0</v>
       </c>
       <c r="C1523" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28054,10 +28054,10 @@
         <v>0</v>
       </c>
       <c r="C1524" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28076,7 +28076,7 @@
         <v>0</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28095,7 +28095,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28114,7 +28114,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28133,7 +28133,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28150,7 +28150,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28169,7 +28169,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28188,7 +28188,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28205,7 +28205,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28224,7 +28224,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28243,7 +28243,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28262,7 +28262,7 @@
         <v>0</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28281,7 +28281,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28300,7 +28300,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28319,7 +28319,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28338,7 +28338,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28355,7 +28355,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.6</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28410,7 +28410,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.6</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28429,7 +28429,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.6</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28448,7 +28448,7 @@
         <v>-1</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28465,7 +28465,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28477,15 +28477,36 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="B1547" t="inlineStr"/>
+      <c r="B1547" t="n">
+        <v>0</v>
+      </c>
       <c r="C1547" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1547" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E1547" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1548" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1548" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D1548" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="E1547" t="b">
-        <v>0</v>
+      <c r="E1548" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -28518,7 +28539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-03-29 | Publication days: 908</t>
+          <t>Coverage: 2022-01-04 to 2026-03-30 | Publication days: 910</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1548"/>
+  <dimension ref="A1:E1549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28218,13 +28218,13 @@
         </is>
       </c>
       <c r="B1533" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1533" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28240,10 +28240,10 @@
         <v>0</v>
       </c>
       <c r="C1534" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28259,10 +28259,10 @@
         <v>0</v>
       </c>
       <c r="C1535" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28278,10 +28278,10 @@
         <v>-3</v>
       </c>
       <c r="C1536" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28297,10 +28297,10 @@
         <v>0</v>
       </c>
       <c r="C1537" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28316,10 +28316,10 @@
         <v>0</v>
       </c>
       <c r="C1538" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28335,10 +28335,10 @@
         <v>-3</v>
       </c>
       <c r="C1539" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28355,7 +28355,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.8</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28410,7 +28410,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28429,7 +28429,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28442,13 +28442,13 @@
         </is>
       </c>
       <c r="B1545" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1545" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.6</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28462,10 +28462,10 @@
       </c>
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28481,10 +28481,10 @@
         <v>0</v>
       </c>
       <c r="C1547" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -28497,15 +28497,34 @@
         </is>
       </c>
       <c r="B1548" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1548" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1548" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1548" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1549" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1549" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D1549" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E1549" t="b">
         <v>1</v>
       </c>
     </row>
@@ -28539,7 +28558,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-03-30 | Publication days: 910</t>
+          <t>Coverage: 2022-01-04 to 2026-03-31 | Publication days: 911</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1549"/>
+  <dimension ref="A1:E1550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27252,13 +27252,13 @@
         </is>
       </c>
       <c r="B1481" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1481" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1481" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1481" t="b">
         <v>1</v>
@@ -27274,10 +27274,10 @@
         <v>3</v>
       </c>
       <c r="C1482" t="n">
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D1482" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1482" t="b">
         <v>1</v>
@@ -27291,10 +27291,10 @@
       </c>
       <c r="B1483" t="inlineStr"/>
       <c r="C1483" t="n">
-        <v>1.428571428571429</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1483" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1483" t="b">
         <v>0</v>
@@ -27308,10 +27308,10 @@
       </c>
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="n">
-        <v>1.857142857142857</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="D1484" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1484" t="b">
         <v>0</v>
@@ -27327,10 +27327,10 @@
         <v>-3</v>
       </c>
       <c r="C1485" t="n">
-        <v>1.428571428571429</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1485" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1485" t="b">
         <v>1</v>
@@ -27346,10 +27346,10 @@
         <v>0</v>
       </c>
       <c r="C1486" t="n">
-        <v>1.142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1486" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1486" t="b">
         <v>1</v>
@@ -27365,10 +27365,10 @@
         <v>0</v>
       </c>
       <c r="C1487" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1487" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27387,7 +27387,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1488" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -27406,7 +27406,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1489" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1489" t="b">
         <v>1</v>
@@ -27423,7 +27423,7 @@
         <v>0</v>
       </c>
       <c r="D1490" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1490" t="b">
         <v>0</v>
@@ -27442,7 +27442,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1491" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1491" t="b">
         <v>1</v>
@@ -27459,7 +27459,7 @@
         <v>0</v>
       </c>
       <c r="D1492" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1492" t="b">
         <v>0</v>
@@ -27478,7 +27478,7 @@
         <v>0</v>
       </c>
       <c r="D1493" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1493" t="b">
         <v>1</v>
@@ -27497,7 +27497,7 @@
         <v>0</v>
       </c>
       <c r="D1494" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1494" t="b">
         <v>1</v>
@@ -27516,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="D1495" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1495" t="b">
         <v>1</v>
@@ -27535,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="D1496" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1496" t="b">
         <v>1</v>
@@ -27552,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="D1497" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1497" t="b">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="D1498" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1498" t="b">
         <v>0</v>
@@ -27588,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="D1499" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1499" t="b">
         <v>1</v>
@@ -27607,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="D1500" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1500" t="b">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="D1501" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1501" t="b">
         <v>1</v>
@@ -27645,7 +27645,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1502" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27664,7 +27664,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1503" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27683,7 +27683,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1504" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27700,7 +27700,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1505" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27719,7 +27719,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1506" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27732,13 +27732,13 @@
         </is>
       </c>
       <c r="B1507" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C1507" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="D1507" t="n">
-        <v>0.3</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27754,10 +27754,10 @@
         <v>-2</v>
       </c>
       <c r="C1508" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1508" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27773,10 +27773,10 @@
         <v>0</v>
       </c>
       <c r="C1509" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1509" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27792,10 +27792,10 @@
         <v>0</v>
       </c>
       <c r="C1510" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1510" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27811,10 +27811,10 @@
         <v>0</v>
       </c>
       <c r="C1511" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1511" t="n">
-        <v>0.1</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27830,10 +27830,10 @@
         <v>2</v>
       </c>
       <c r="C1512" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1512" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27849,10 +27849,10 @@
         <v>-2</v>
       </c>
       <c r="C1513" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.1</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27871,7 +27871,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.2</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1514" t="b">
         <v>1</v>
@@ -27888,7 +27888,7 @@
         <v>0</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.1</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27907,7 +27907,7 @@
         <v>0</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.1</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27926,7 +27926,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.2</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27943,7 +27943,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.3</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27962,7 +27962,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27981,7 +27981,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -28000,7 +28000,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28019,7 +28019,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28038,7 +28038,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28057,7 +28057,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28076,7 +28076,7 @@
         <v>0</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.3</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28095,7 +28095,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.3</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28114,7 +28114,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.3</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28133,7 +28133,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28150,7 +28150,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28169,7 +28169,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28188,7 +28188,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28205,7 +28205,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.5</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28218,13 +28218,13 @@
         </is>
       </c>
       <c r="B1533" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1533" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28240,10 +28240,10 @@
         <v>0</v>
       </c>
       <c r="C1534" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28259,10 +28259,10 @@
         <v>0</v>
       </c>
       <c r="C1535" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28278,10 +28278,10 @@
         <v>-3</v>
       </c>
       <c r="C1536" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28297,10 +28297,10 @@
         <v>0</v>
       </c>
       <c r="C1537" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.5</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28316,10 +28316,10 @@
         <v>0</v>
       </c>
       <c r="C1538" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28335,10 +28335,10 @@
         <v>-3</v>
       </c>
       <c r="C1539" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28355,7 +28355,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.8</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28410,7 +28410,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28429,7 +28429,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28442,13 +28442,13 @@
         </is>
       </c>
       <c r="B1545" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1545" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28462,10 +28462,10 @@
       </c>
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28481,10 +28481,10 @@
         <v>0</v>
       </c>
       <c r="C1547" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -28500,10 +28500,10 @@
         <v>-2</v>
       </c>
       <c r="C1548" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1548" t="n">
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="E1548" t="b">
         <v>1</v>
@@ -28519,12 +28519,31 @@
         <v>0</v>
       </c>
       <c r="C1549" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1549" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="E1549" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1550" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1550" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D1550" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E1550" t="b">
         <v>1</v>
       </c>
     </row>
@@ -28558,7 +28577,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-03-31 | Publication days: 911</t>
+          <t>Coverage: 2022-01-04 to 2026-04-01 | Publication days: 912</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1550"/>
+  <dimension ref="A1:E1551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27362,13 +27362,13 @@
         </is>
       </c>
       <c r="B1487" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1487" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1487" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27384,10 +27384,10 @@
         <v>0</v>
       </c>
       <c r="C1488" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1488" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -27403,10 +27403,10 @@
         <v>0</v>
       </c>
       <c r="C1489" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1489" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1489" t="b">
         <v>1</v>
@@ -27420,10 +27420,10 @@
       </c>
       <c r="B1490" t="inlineStr"/>
       <c r="C1490" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1490" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1490" t="b">
         <v>0</v>
@@ -27439,10 +27439,10 @@
         <v>0</v>
       </c>
       <c r="C1491" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1491" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1491" t="b">
         <v>1</v>
@@ -27456,10 +27456,10 @@
       </c>
       <c r="B1492" t="inlineStr"/>
       <c r="C1492" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1492" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1492" t="b">
         <v>0</v>
@@ -27475,10 +27475,10 @@
         <v>0</v>
       </c>
       <c r="C1493" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1493" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1493" t="b">
         <v>1</v>
@@ -27497,7 +27497,7 @@
         <v>0</v>
       </c>
       <c r="D1494" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1494" t="b">
         <v>1</v>
@@ -27516,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="D1495" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1495" t="b">
         <v>1</v>
@@ -27535,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="D1496" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1496" t="b">
         <v>1</v>
@@ -27552,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="D1497" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1497" t="b">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="D1498" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1498" t="b">
         <v>0</v>
@@ -27588,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="D1499" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1499" t="b">
         <v>1</v>
@@ -27607,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="D1500" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1500" t="b">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="D1501" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1501" t="b">
         <v>1</v>
@@ -27645,7 +27645,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1502" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27664,7 +27664,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1503" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27683,7 +27683,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1504" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27700,7 +27700,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1505" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27719,7 +27719,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1506" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27732,13 +27732,13 @@
         </is>
       </c>
       <c r="B1507" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C1507" t="n">
-        <v>0</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1507" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27754,10 +27754,10 @@
         <v>-2</v>
       </c>
       <c r="C1508" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1508" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27773,10 +27773,10 @@
         <v>0</v>
       </c>
       <c r="C1509" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1509" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27792,10 +27792,10 @@
         <v>0</v>
       </c>
       <c r="C1510" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1510" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27811,10 +27811,10 @@
         <v>0</v>
       </c>
       <c r="C1511" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1511" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27830,10 +27830,10 @@
         <v>2</v>
       </c>
       <c r="C1512" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1512" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27849,10 +27849,10 @@
         <v>-2</v>
       </c>
       <c r="C1513" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27871,7 +27871,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1514" t="b">
         <v>1</v>
@@ -27888,7 +27888,7 @@
         <v>0</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27907,7 +27907,7 @@
         <v>0</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27926,7 +27926,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27943,7 +27943,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27962,7 +27962,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27981,7 +27981,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -28000,7 +28000,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28019,7 +28019,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28038,7 +28038,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28057,7 +28057,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28076,7 +28076,7 @@
         <v>0</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28095,7 +28095,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28114,7 +28114,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28127,13 +28127,13 @@
         </is>
       </c>
       <c r="B1528" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1528" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28147,10 +28147,10 @@
       </c>
       <c r="B1529" t="inlineStr"/>
       <c r="C1529" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28166,10 +28166,10 @@
         <v>0</v>
       </c>
       <c r="C1530" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="C1531" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28202,10 +28202,10 @@
       </c>
       <c r="B1532" t="inlineStr"/>
       <c r="C1532" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28221,10 +28221,10 @@
         <v>2</v>
       </c>
       <c r="C1533" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28240,10 +28240,10 @@
         <v>0</v>
       </c>
       <c r="C1534" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28259,10 +28259,10 @@
         <v>0</v>
       </c>
       <c r="C1535" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="B1536" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C1536" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.5</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28297,10 +28297,10 @@
         <v>0</v>
       </c>
       <c r="C1537" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28316,10 +28316,10 @@
         <v>0</v>
       </c>
       <c r="C1538" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.2</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28332,13 +28332,13 @@
         </is>
       </c>
       <c r="B1539" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C1539" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28352,10 +28352,10 @@
       </c>
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28369,10 +28369,10 @@
       </c>
       <c r="B1541" t="inlineStr"/>
       <c r="C1541" t="n">
-        <v>-1.714285714285714</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28388,10 +28388,10 @@
         <v>0</v>
       </c>
       <c r="C1542" t="n">
-        <v>-1.714285714285714</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28407,10 +28407,10 @@
         <v>0</v>
       </c>
       <c r="C1543" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="C1544" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28445,10 +28445,10 @@
         <v>2</v>
       </c>
       <c r="C1545" t="n">
-        <v>-1</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.6</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28462,10 +28462,10 @@
       </c>
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28481,10 +28481,10 @@
         <v>0</v>
       </c>
       <c r="C1547" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -28503,7 +28503,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1548" t="n">
-        <v>-0.4</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1548" t="b">
         <v>1</v>
@@ -28516,13 +28516,13 @@
         </is>
       </c>
       <c r="B1549" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1549" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1549" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E1549" t="b">
         <v>1</v>
@@ -28538,12 +28538,31 @@
         <v>0</v>
       </c>
       <c r="C1550" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1550" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E1550" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1551" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1551" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1551" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E1551" t="b">
         <v>1</v>
       </c>
     </row>
@@ -28577,7 +28596,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-04-01 | Publication days: 912</t>
+          <t>Coverage: 2022-01-04 to 2026-04-02 | Publication days: 913</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1551"/>
+  <dimension ref="A1:E1552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27639,13 +27639,13 @@
         </is>
       </c>
       <c r="B1502" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1502" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1502" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27661,10 +27661,10 @@
         <v>0</v>
       </c>
       <c r="C1503" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1503" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27680,10 +27680,10 @@
         <v>0</v>
       </c>
       <c r="C1504" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1504" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27697,10 +27697,10 @@
       </c>
       <c r="B1505" t="inlineStr"/>
       <c r="C1505" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1505" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27716,10 +27716,10 @@
         <v>0</v>
       </c>
       <c r="C1506" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1506" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27735,10 +27735,10 @@
         <v>-3</v>
       </c>
       <c r="C1507" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1507" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27754,10 +27754,10 @@
         <v>-2</v>
       </c>
       <c r="C1508" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1508" t="n">
-        <v>0.1</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27776,7 +27776,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1509" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27795,7 +27795,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1510" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27814,7 +27814,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1511" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27833,7 +27833,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1512" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27852,7 +27852,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27871,7 +27871,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1514" t="b">
         <v>1</v>
@@ -27888,7 +27888,7 @@
         <v>0</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27907,7 +27907,7 @@
         <v>0</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27926,7 +27926,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27943,7 +27943,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27962,7 +27962,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27981,7 +27981,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -28000,7 +28000,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28019,7 +28019,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28038,7 +28038,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28057,7 +28057,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28076,7 +28076,7 @@
         <v>0</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28095,7 +28095,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28114,7 +28114,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28127,13 +28127,13 @@
         </is>
       </c>
       <c r="B1528" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1528" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.3</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28147,10 +28147,10 @@
       </c>
       <c r="B1529" t="inlineStr"/>
       <c r="C1529" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.3</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28166,10 +28166,10 @@
         <v>0</v>
       </c>
       <c r="C1530" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.3</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="C1531" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.3</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28202,10 +28202,10 @@
       </c>
       <c r="B1532" t="inlineStr"/>
       <c r="C1532" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28221,10 +28221,10 @@
         <v>2</v>
       </c>
       <c r="C1533" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28240,10 +28240,10 @@
         <v>0</v>
       </c>
       <c r="C1534" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28259,10 +28259,10 @@
         <v>0</v>
       </c>
       <c r="C1535" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28281,7 +28281,7 @@
         <v>0</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28300,7 +28300,7 @@
         <v>0</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28319,7 +28319,7 @@
         <v>0</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28332,13 +28332,13 @@
         </is>
       </c>
       <c r="B1539" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C1539" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28352,10 +28352,10 @@
       </c>
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28369,10 +28369,10 @@
       </c>
       <c r="B1541" t="inlineStr"/>
       <c r="C1541" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28388,10 +28388,10 @@
         <v>0</v>
       </c>
       <c r="C1542" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28407,10 +28407,10 @@
         <v>0</v>
       </c>
       <c r="C1543" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="C1544" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28445,10 +28445,10 @@
         <v>2</v>
       </c>
       <c r="C1545" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28462,10 +28462,10 @@
       </c>
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28481,10 +28481,10 @@
         <v>0</v>
       </c>
       <c r="C1547" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -28503,7 +28503,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1548" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1548" t="b">
         <v>1</v>
@@ -28522,7 +28522,7 @@
         <v>0</v>
       </c>
       <c r="D1549" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E1549" t="b">
         <v>1</v>
@@ -28541,7 +28541,7 @@
         <v>0</v>
       </c>
       <c r="D1550" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E1550" t="b">
         <v>1</v>
@@ -28560,10 +28560,27 @@
         <v>0</v>
       </c>
       <c r="D1551" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E1551" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr"/>
+      <c r="C1552" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D1552" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E1552" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -28596,7 +28613,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-04-02 | Publication days: 913</t>
+          <t>Coverage: 2022-01-04 to 2026-04-03 | Publication days: 913</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1552"/>
+  <dimension ref="A1:E1553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27639,13 +27639,13 @@
         </is>
       </c>
       <c r="B1502" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1502" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1502" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27661,10 +27661,10 @@
         <v>0</v>
       </c>
       <c r="C1503" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1503" t="n">
-        <v>0.2</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27680,10 +27680,10 @@
         <v>0</v>
       </c>
       <c r="C1504" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1504" t="n">
-        <v>0.2</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27697,10 +27697,10 @@
       </c>
       <c r="B1505" t="inlineStr"/>
       <c r="C1505" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1505" t="n">
-        <v>0.2</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27716,10 +27716,10 @@
         <v>0</v>
       </c>
       <c r="C1506" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1506" t="n">
-        <v>0.2</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27735,10 +27735,10 @@
         <v>-3</v>
       </c>
       <c r="C1507" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1507" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27754,10 +27754,10 @@
         <v>-2</v>
       </c>
       <c r="C1508" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1508" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27776,7 +27776,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1509" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27795,7 +27795,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1510" t="n">
-        <v>-0.1</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27814,7 +27814,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1511" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27833,7 +27833,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1512" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27852,7 +27852,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27871,7 +27871,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1514" t="b">
         <v>1</v>
@@ -27888,7 +27888,7 @@
         <v>0</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27907,7 +27907,7 @@
         <v>0</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27926,7 +27926,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27943,7 +27943,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27962,7 +27962,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27981,7 +27981,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -28000,7 +28000,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28019,7 +28019,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28038,7 +28038,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28057,7 +28057,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28076,7 +28076,7 @@
         <v>0</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28095,7 +28095,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28114,7 +28114,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28133,7 +28133,7 @@
         <v>0</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28150,7 +28150,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28169,7 +28169,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28188,7 +28188,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28218,13 +28218,13 @@
         </is>
       </c>
       <c r="B1533" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1533" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28240,10 +28240,10 @@
         <v>0</v>
       </c>
       <c r="C1534" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28259,10 +28259,10 @@
         <v>0</v>
       </c>
       <c r="C1535" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28278,10 +28278,10 @@
         <v>-2</v>
       </c>
       <c r="C1536" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28297,10 +28297,10 @@
         <v>0</v>
       </c>
       <c r="C1537" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28316,10 +28316,10 @@
         <v>0</v>
       </c>
       <c r="C1538" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28335,10 +28335,10 @@
         <v>-3</v>
       </c>
       <c r="C1539" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28355,7 +28355,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.6</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.7</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="B1543" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1543" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="C1544" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28445,10 +28445,10 @@
         <v>2</v>
       </c>
       <c r="C1545" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28462,10 +28462,10 @@
       </c>
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28481,10 +28481,10 @@
         <v>0</v>
       </c>
       <c r="C1547" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -28500,10 +28500,10 @@
         <v>-2</v>
       </c>
       <c r="C1548" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1548" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1548" t="b">
         <v>1</v>
@@ -28519,10 +28519,10 @@
         <v>-2</v>
       </c>
       <c r="C1549" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1549" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1549" t="b">
         <v>1</v>
@@ -28541,7 +28541,7 @@
         <v>0</v>
       </c>
       <c r="D1550" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1550" t="b">
         <v>1</v>
@@ -28560,7 +28560,7 @@
         <v>0</v>
       </c>
       <c r="D1551" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1551" t="b">
         <v>1</v>
@@ -28577,9 +28577,26 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1552" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1552" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr"/>
+      <c r="C1553" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D1553" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E1553" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28613,7 +28630,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-04-03 | Publication days: 913</t>
+          <t>Coverage: 2022-01-04 to 2026-04-04 | Publication days: 913</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1553"/>
+  <dimension ref="A1:E1554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28070,13 +28070,13 @@
         </is>
       </c>
       <c r="B1525" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="C1525" t="n">
-        <v>0</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.3</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28092,10 +28092,10 @@
         <v>0</v>
       </c>
       <c r="C1526" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.3</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28111,10 +28111,10 @@
         <v>0</v>
       </c>
       <c r="C1527" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.3</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28127,13 +28127,13 @@
         </is>
       </c>
       <c r="B1528" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1528" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28147,10 +28147,10 @@
       </c>
       <c r="B1529" t="inlineStr"/>
       <c r="C1529" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.5</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28166,10 +28166,10 @@
         <v>0</v>
       </c>
       <c r="C1530" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.5</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="C1531" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.5</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28202,10 +28202,10 @@
       </c>
       <c r="B1532" t="inlineStr"/>
       <c r="C1532" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28218,13 +28218,13 @@
         </is>
       </c>
       <c r="B1533" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1533" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28240,10 +28240,10 @@
         <v>0</v>
       </c>
       <c r="C1534" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28259,10 +28259,10 @@
         <v>0</v>
       </c>
       <c r="C1535" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28278,10 +28278,10 @@
         <v>-2</v>
       </c>
       <c r="C1536" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28297,10 +28297,10 @@
         <v>0</v>
       </c>
       <c r="C1537" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28316,10 +28316,10 @@
         <v>0</v>
       </c>
       <c r="C1538" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28335,10 +28335,10 @@
         <v>-3</v>
       </c>
       <c r="C1539" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28355,7 +28355,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28410,7 +28410,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28429,7 +28429,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28442,13 +28442,13 @@
         </is>
       </c>
       <c r="B1545" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1545" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28462,10 +28462,10 @@
       </c>
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28481,10 +28481,10 @@
         <v>0</v>
       </c>
       <c r="C1547" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.6</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -28500,10 +28500,10 @@
         <v>-2</v>
       </c>
       <c r="C1548" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1548" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1548" t="b">
         <v>1</v>
@@ -28519,10 +28519,10 @@
         <v>-2</v>
       </c>
       <c r="C1549" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1549" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1549" t="b">
         <v>1</v>
@@ -28538,10 +28538,10 @@
         <v>0</v>
       </c>
       <c r="C1550" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1550" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1550" t="b">
         <v>1</v>
@@ -28557,10 +28557,10 @@
         <v>0</v>
       </c>
       <c r="C1551" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1551" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1551" t="b">
         <v>1</v>
@@ -28574,10 +28574,10 @@
       </c>
       <c r="B1552" t="inlineStr"/>
       <c r="C1552" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1552" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1552" t="b">
         <v>0</v>
@@ -28594,9 +28594,26 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1553" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1553" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr"/>
+      <c r="C1554" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D1554" t="n">
+        <v>-0.5666666666666667</v>
+      </c>
+      <c r="E1554" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28630,7 +28647,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-04-04 | Publication days: 913</t>
+          <t>Coverage: 2022-01-04 to 2026-04-05 | Publication days: 913</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1554"/>
+  <dimension ref="A1:E1555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28614,6 +28614,23 @@
         <v>-0.5666666666666667</v>
       </c>
       <c r="E1554" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr"/>
+      <c r="C1555" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D1555" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E1555" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28647,7 +28664,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-04-05 | Publication days: 913</t>
+          <t>Coverage: 2022-01-04 to 2026-04-06 | Publication days: 913</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1555"/>
+  <dimension ref="A1:E1556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27271,13 +27271,13 @@
         </is>
       </c>
       <c r="B1482" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1482" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1482" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1482" t="b">
         <v>1</v>
@@ -27291,10 +27291,10 @@
       </c>
       <c r="B1483" t="inlineStr"/>
       <c r="C1483" t="n">
-        <v>1.142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1483" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1483" t="b">
         <v>0</v>
@@ -27308,10 +27308,10 @@
       </c>
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="n">
-        <v>1.571428571428571</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1484" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1484" t="b">
         <v>0</v>
@@ -27327,10 +27327,10 @@
         <v>-3</v>
       </c>
       <c r="C1485" t="n">
-        <v>1.142857142857143</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D1485" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1485" t="b">
         <v>1</v>
@@ -27346,10 +27346,10 @@
         <v>0</v>
       </c>
       <c r="C1486" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1486" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1486" t="b">
         <v>1</v>
@@ -27365,10 +27365,10 @@
         <v>-2</v>
       </c>
       <c r="C1487" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1487" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27384,10 +27384,10 @@
         <v>0</v>
       </c>
       <c r="C1488" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1488" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -27403,10 +27403,10 @@
         <v>0</v>
       </c>
       <c r="C1489" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1489" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1489" t="b">
         <v>1</v>
@@ -27420,10 +27420,10 @@
       </c>
       <c r="B1490" t="inlineStr"/>
       <c r="C1490" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1490" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1490" t="b">
         <v>0</v>
@@ -27442,7 +27442,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1491" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1491" t="b">
         <v>1</v>
@@ -27459,7 +27459,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1492" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1492" t="b">
         <v>0</v>
@@ -27478,7 +27478,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1493" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1493" t="b">
         <v>1</v>
@@ -27497,7 +27497,7 @@
         <v>0</v>
       </c>
       <c r="D1494" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1494" t="b">
         <v>1</v>
@@ -27516,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="D1495" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1495" t="b">
         <v>1</v>
@@ -27535,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="D1496" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1496" t="b">
         <v>1</v>
@@ -27552,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="D1497" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1497" t="b">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="D1498" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1498" t="b">
         <v>0</v>
@@ -27588,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="D1499" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1499" t="b">
         <v>1</v>
@@ -27607,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="D1500" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1500" t="b">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="D1501" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1501" t="b">
         <v>1</v>
@@ -27645,7 +27645,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1502" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27664,7 +27664,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1503" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27683,7 +27683,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1504" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27700,7 +27700,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1505" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27719,7 +27719,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1506" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27738,7 +27738,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1507" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27757,7 +27757,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1508" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27776,7 +27776,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1509" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27795,7 +27795,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1510" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27814,7 +27814,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1511" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27833,7 +27833,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1512" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27852,7 +27852,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27920,13 +27920,13 @@
         </is>
       </c>
       <c r="B1517" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C1517" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.2</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27940,10 +27940,10 @@
       </c>
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27959,10 +27959,10 @@
         <v>-3</v>
       </c>
       <c r="C1519" t="n">
-        <v>-1.571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27978,10 +27978,10 @@
         <v>0</v>
       </c>
       <c r="C1520" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -27997,10 +27997,10 @@
         <v>0</v>
       </c>
       <c r="C1521" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28016,10 +28016,10 @@
         <v>0</v>
       </c>
       <c r="C1522" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28035,10 +28035,10 @@
         <v>0</v>
       </c>
       <c r="C1523" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28054,10 +28054,10 @@
         <v>0</v>
       </c>
       <c r="C1524" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28076,7 +28076,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28095,7 +28095,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28114,7 +28114,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28133,7 +28133,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28150,7 +28150,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28169,7 +28169,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28188,7 +28188,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28205,7 +28205,7 @@
         <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28224,7 +28224,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28243,7 +28243,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28262,7 +28262,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28281,7 +28281,7 @@
         <v>0</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28300,7 +28300,7 @@
         <v>0</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28319,7 +28319,7 @@
         <v>0</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28338,7 +28338,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28355,7 +28355,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.6</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28410,7 +28410,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28429,7 +28429,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28448,7 +28448,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28465,7 +28465,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28484,7 +28484,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -28572,7 +28572,9 @@
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="B1552" t="inlineStr"/>
+      <c r="B1552" t="n">
+        <v>0</v>
+      </c>
       <c r="C1552" t="n">
         <v>-0.5714285714285714</v>
       </c>
@@ -28580,7 +28582,7 @@
         <v>-0.5666666666666667</v>
       </c>
       <c r="E1552" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1553">
@@ -28589,7 +28591,9 @@
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="B1553" t="inlineStr"/>
+      <c r="B1553" t="n">
+        <v>0</v>
+      </c>
       <c r="C1553" t="n">
         <v>-0.5714285714285714</v>
       </c>
@@ -28597,7 +28601,7 @@
         <v>-0.5666666666666667</v>
       </c>
       <c r="E1553" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1554">
@@ -28631,6 +28635,23 @@
         <v>-0.5</v>
       </c>
       <c r="E1555" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr"/>
+      <c r="C1556" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1556" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E1556" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28664,7 +28685,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-04-06 | Publication days: 913</t>
+          <t>Coverage: 2022-01-04 to 2026-04-07 | Publication days: 915</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1556"/>
+  <dimension ref="A1:E1557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27216,13 +27216,13 @@
         </is>
       </c>
       <c r="B1479" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1479" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1479" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1479" t="b">
         <v>1</v>
@@ -27236,10 +27236,10 @@
       </c>
       <c r="B1480" t="inlineStr"/>
       <c r="C1480" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1480" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1480" t="b">
         <v>0</v>
@@ -27255,10 +27255,10 @@
         <v>-2</v>
       </c>
       <c r="C1481" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1481" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1481" t="b">
         <v>1</v>
@@ -27274,10 +27274,10 @@
         <v>2</v>
       </c>
       <c r="C1482" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1482" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1482" t="b">
         <v>1</v>
@@ -27291,10 +27291,10 @@
       </c>
       <c r="B1483" t="inlineStr"/>
       <c r="C1483" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1483" t="n">
-        <v>0.1</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1483" t="b">
         <v>0</v>
@@ -27308,10 +27308,10 @@
       </c>
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="n">
-        <v>1.142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1484" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1484" t="b">
         <v>0</v>
@@ -27327,10 +27327,10 @@
         <v>-3</v>
       </c>
       <c r="C1485" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1485" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1485" t="b">
         <v>1</v>
@@ -27346,10 +27346,10 @@
         <v>0</v>
       </c>
       <c r="C1486" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1486" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1486" t="b">
         <v>1</v>
@@ -27368,7 +27368,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1487" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27387,7 +27387,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="D1488" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -27406,7 +27406,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1489" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1489" t="b">
         <v>1</v>
@@ -27423,7 +27423,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1490" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1490" t="b">
         <v>0</v>
@@ -27442,7 +27442,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1491" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1491" t="b">
         <v>1</v>
@@ -27459,7 +27459,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1492" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1492" t="b">
         <v>0</v>
@@ -27478,7 +27478,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1493" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1493" t="b">
         <v>1</v>
@@ -27497,7 +27497,7 @@
         <v>0</v>
       </c>
       <c r="D1494" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1494" t="b">
         <v>1</v>
@@ -27516,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="D1495" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1495" t="b">
         <v>1</v>
@@ -27535,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="D1496" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1496" t="b">
         <v>1</v>
@@ -27552,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="D1497" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1497" t="b">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="D1498" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1498" t="b">
         <v>0</v>
@@ -27588,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="D1499" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1499" t="b">
         <v>1</v>
@@ -27607,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="D1500" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1500" t="b">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="D1501" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1501" t="b">
         <v>1</v>
@@ -27645,7 +27645,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1502" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27664,7 +27664,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1503" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27683,7 +27683,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1504" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27700,7 +27700,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1505" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27719,7 +27719,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1506" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27738,7 +27738,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="D1507" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27757,7 +27757,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1508" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27776,7 +27776,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1509" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27920,13 +27920,13 @@
         </is>
       </c>
       <c r="B1517" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C1517" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27940,10 +27940,10 @@
       </c>
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27959,10 +27959,10 @@
         <v>-3</v>
       </c>
       <c r="C1519" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27978,10 +27978,10 @@
         <v>0</v>
       </c>
       <c r="C1520" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -27997,10 +27997,10 @@
         <v>0</v>
       </c>
       <c r="C1521" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28016,10 +28016,10 @@
         <v>0</v>
       </c>
       <c r="C1522" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28035,10 +28035,10 @@
         <v>0</v>
       </c>
       <c r="C1523" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28054,10 +28054,10 @@
         <v>0</v>
       </c>
       <c r="C1524" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28076,7 +28076,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28095,7 +28095,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28114,7 +28114,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28133,7 +28133,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28150,7 +28150,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28169,7 +28169,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28188,7 +28188,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28205,7 +28205,7 @@
         <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28224,7 +28224,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28243,7 +28243,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28262,7 +28262,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28281,7 +28281,7 @@
         <v>0</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28300,7 +28300,7 @@
         <v>0</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28319,7 +28319,7 @@
         <v>0</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28338,7 +28338,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28355,7 +28355,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.6</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28410,7 +28410,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28429,7 +28429,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28448,7 +28448,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28465,7 +28465,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28484,7 +28484,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.6</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -28653,6 +28653,25 @@
       </c>
       <c r="E1556" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1557" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1557" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1557" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E1557" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -28685,7 +28704,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-04-07 | Publication days: 915</t>
+          <t>Coverage: 2022-01-04 to 2026-04-08 | Publication days: 916</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1557"/>
+  <dimension ref="A1:E1558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27197,13 +27197,13 @@
         </is>
       </c>
       <c r="B1478" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1478" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1478" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E1478" t="b">
         <v>1</v>
@@ -27219,10 +27219,10 @@
         <v>0</v>
       </c>
       <c r="C1479" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1479" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E1479" t="b">
         <v>1</v>
@@ -27236,10 +27236,10 @@
       </c>
       <c r="B1480" t="inlineStr"/>
       <c r="C1480" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1480" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E1480" t="b">
         <v>0</v>
@@ -27255,10 +27255,10 @@
         <v>-2</v>
       </c>
       <c r="C1481" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1481" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1481" t="b">
         <v>1</v>
@@ -27271,13 +27271,13 @@
         </is>
       </c>
       <c r="B1482" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="C1482" t="n">
-        <v>0</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1482" t="n">
-        <v>-0.1</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1482" t="b">
         <v>1</v>
@@ -27291,10 +27291,10 @@
       </c>
       <c r="B1483" t="inlineStr"/>
       <c r="C1483" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1483" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1483" t="b">
         <v>0</v>
@@ -27308,10 +27308,10 @@
       </c>
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1484" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1484" t="b">
         <v>0</v>
@@ -27327,10 +27327,10 @@
         <v>-3</v>
       </c>
       <c r="C1485" t="n">
-        <v>0.1428571428571428</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1485" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1485" t="b">
         <v>1</v>
@@ -27346,10 +27346,10 @@
         <v>0</v>
       </c>
       <c r="C1486" t="n">
-        <v>0.1428571428571428</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1486" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1486" t="b">
         <v>1</v>
@@ -27365,10 +27365,10 @@
         <v>-2</v>
       </c>
       <c r="C1487" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D1487" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27384,10 +27384,10 @@
         <v>0</v>
       </c>
       <c r="C1488" t="n">
-        <v>0.1428571428571428</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1488" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -27403,10 +27403,10 @@
         <v>0</v>
       </c>
       <c r="C1489" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1489" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1489" t="b">
         <v>1</v>
@@ -27420,10 +27420,10 @@
       </c>
       <c r="B1490" t="inlineStr"/>
       <c r="C1490" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-1</v>
       </c>
       <c r="D1490" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1490" t="b">
         <v>0</v>
@@ -27442,7 +27442,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1491" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1491" t="b">
         <v>1</v>
@@ -27459,7 +27459,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1492" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1492" t="b">
         <v>0</v>
@@ -27478,7 +27478,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1493" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1493" t="b">
         <v>1</v>
@@ -27497,7 +27497,7 @@
         <v>0</v>
       </c>
       <c r="D1494" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1494" t="b">
         <v>1</v>
@@ -27516,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="D1495" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1495" t="b">
         <v>1</v>
@@ -27535,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="D1496" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1496" t="b">
         <v>1</v>
@@ -27552,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="D1497" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1497" t="b">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="D1498" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1498" t="b">
         <v>0</v>
@@ -27588,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="D1499" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1499" t="b">
         <v>1</v>
@@ -27607,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="D1500" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1500" t="b">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="D1501" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1501" t="b">
         <v>1</v>
@@ -27639,13 +27639,13 @@
         </is>
       </c>
       <c r="B1502" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1502" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1502" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27661,10 +27661,10 @@
         <v>0</v>
       </c>
       <c r="C1503" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1503" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27680,10 +27680,10 @@
         <v>0</v>
       </c>
       <c r="C1504" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1504" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27697,10 +27697,10 @@
       </c>
       <c r="B1505" t="inlineStr"/>
       <c r="C1505" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1505" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27716,10 +27716,10 @@
         <v>0</v>
       </c>
       <c r="C1506" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1506" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27735,10 +27735,10 @@
         <v>-3</v>
       </c>
       <c r="C1507" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1507" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27754,10 +27754,10 @@
         <v>-2</v>
       </c>
       <c r="C1508" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1508" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27776,7 +27776,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1509" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27795,7 +27795,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1510" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27814,7 +27814,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1511" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27827,13 +27827,13 @@
         </is>
       </c>
       <c r="B1512" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1512" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1512" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27849,10 +27849,10 @@
         <v>-2</v>
       </c>
       <c r="C1513" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.2</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27868,10 +27868,10 @@
         <v>0</v>
       </c>
       <c r="C1514" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1514" t="b">
         <v>1</v>
@@ -27885,10 +27885,10 @@
       </c>
       <c r="B1515" t="inlineStr"/>
       <c r="C1515" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27904,10 +27904,10 @@
         <v>0</v>
       </c>
       <c r="C1516" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27923,10 +27923,10 @@
         <v>-3</v>
       </c>
       <c r="C1517" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27940,10 +27940,10 @@
       </c>
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.3</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27962,7 +27962,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27981,7 +27981,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -28000,7 +28000,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28019,7 +28019,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28038,7 +28038,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28057,7 +28057,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28070,13 +28070,13 @@
         </is>
       </c>
       <c r="B1525" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="C1525" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28092,10 +28092,10 @@
         <v>0</v>
       </c>
       <c r="C1526" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28111,10 +28111,10 @@
         <v>0</v>
       </c>
       <c r="C1527" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28130,10 +28130,10 @@
         <v>0</v>
       </c>
       <c r="C1528" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28147,10 +28147,10 @@
       </c>
       <c r="B1529" t="inlineStr"/>
       <c r="C1529" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28166,10 +28166,10 @@
         <v>0</v>
       </c>
       <c r="C1530" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="C1531" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28205,7 +28205,7 @@
         <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28218,13 +28218,13 @@
         </is>
       </c>
       <c r="B1533" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1533" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28240,10 +28240,10 @@
         <v>0</v>
       </c>
       <c r="C1534" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28259,10 +28259,10 @@
         <v>0</v>
       </c>
       <c r="C1535" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28278,10 +28278,10 @@
         <v>-2</v>
       </c>
       <c r="C1536" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28297,10 +28297,10 @@
         <v>0</v>
       </c>
       <c r="C1537" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28316,10 +28316,10 @@
         <v>0</v>
       </c>
       <c r="C1538" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28335,10 +28335,10 @@
         <v>-3</v>
       </c>
       <c r="C1539" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28355,7 +28355,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28410,7 +28410,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28429,7 +28429,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28442,13 +28442,13 @@
         </is>
       </c>
       <c r="B1545" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1545" t="n">
-        <v>-1.571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28462,10 +28462,10 @@
       </c>
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28481,10 +28481,10 @@
         <v>0</v>
       </c>
       <c r="C1547" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -28497,13 +28497,13 @@
         </is>
       </c>
       <c r="B1548" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1548" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1548" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="E1548" t="b">
         <v>1</v>
@@ -28519,10 +28519,10 @@
         <v>-2</v>
       </c>
       <c r="C1549" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1549" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1549" t="b">
         <v>1</v>
@@ -28538,10 +28538,10 @@
         <v>0</v>
       </c>
       <c r="C1550" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1550" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1550" t="b">
         <v>1</v>
@@ -28557,10 +28557,10 @@
         <v>0</v>
       </c>
       <c r="C1551" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1551" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1551" t="b">
         <v>1</v>
@@ -28576,10 +28576,10 @@
         <v>0</v>
       </c>
       <c r="C1552" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1552" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1552" t="b">
         <v>1</v>
@@ -28595,10 +28595,10 @@
         <v>0</v>
       </c>
       <c r="C1553" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1553" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1553" t="b">
         <v>1</v>
@@ -28612,10 +28612,10 @@
       </c>
       <c r="B1554" t="inlineStr"/>
       <c r="C1554" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1554" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1554" t="b">
         <v>0</v>
@@ -28632,7 +28632,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1555" t="n">
-        <v>-0.5</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1555" t="b">
         <v>0</v>
@@ -28649,7 +28649,7 @@
         <v>0</v>
       </c>
       <c r="D1556" t="n">
-        <v>-0.5</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1556" t="b">
         <v>0</v>
@@ -28668,9 +28668,28 @@
         <v>0</v>
       </c>
       <c r="D1557" t="n">
-        <v>-0.5</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1557" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1558" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1558" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D1558" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E1558" t="b">
         <v>1</v>
       </c>
     </row>
@@ -28704,7 +28723,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-04-08 | Publication days: 916</t>
+          <t>Coverage: 2022-01-04 to 2026-04-09 | Publication days: 917</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1558"/>
+  <dimension ref="A1:E1559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27252,13 +27252,13 @@
         </is>
       </c>
       <c r="B1481" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1481" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1481" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.1</v>
       </c>
       <c r="E1481" t="b">
         <v>1</v>
@@ -27271,13 +27271,13 @@
         </is>
       </c>
       <c r="B1482" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="C1482" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D1482" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1482" t="b">
         <v>1</v>
@@ -27291,10 +27291,10 @@
       </c>
       <c r="B1483" t="inlineStr"/>
       <c r="C1483" t="n">
-        <v>-0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="D1483" t="n">
-        <v>-0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1483" t="b">
         <v>0</v>
@@ -27308,10 +27308,10 @@
       </c>
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="n">
-        <v>-0.7142857142857143</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D1484" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E1484" t="b">
         <v>0</v>
@@ -27327,10 +27327,10 @@
         <v>-3</v>
       </c>
       <c r="C1485" t="n">
-        <v>-1.571428571428571</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1485" t="n">
-        <v>-0.3666666666666666</v>
+        <v>0.1</v>
       </c>
       <c r="E1485" t="b">
         <v>1</v>
@@ -27346,10 +27346,10 @@
         <v>0</v>
       </c>
       <c r="C1486" t="n">
-        <v>-1.571428571428571</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1486" t="n">
-        <v>-0.3666666666666666</v>
+        <v>0.1</v>
       </c>
       <c r="E1486" t="b">
         <v>1</v>
@@ -27362,13 +27362,13 @@
         </is>
       </c>
       <c r="B1487" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1487" t="n">
-        <v>-1.857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1487" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1487" t="b">
         <v>1</v>
@@ -27384,10 +27384,10 @@
         <v>0</v>
       </c>
       <c r="C1488" t="n">
-        <v>-1.571428571428571</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1488" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1488" t="b">
         <v>1</v>
@@ -27403,10 +27403,10 @@
         <v>0</v>
       </c>
       <c r="C1489" t="n">
-        <v>-1.285714285714286</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1489" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1489" t="b">
         <v>1</v>
@@ -27420,10 +27420,10 @@
       </c>
       <c r="B1490" t="inlineStr"/>
       <c r="C1490" t="n">
-        <v>-1</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1490" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1490" t="b">
         <v>0</v>
@@ -27439,10 +27439,10 @@
         <v>0</v>
       </c>
       <c r="C1491" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1491" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1491" t="b">
         <v>1</v>
@@ -27456,10 +27456,10 @@
       </c>
       <c r="B1492" t="inlineStr"/>
       <c r="C1492" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1492" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1492" t="b">
         <v>0</v>
@@ -27475,10 +27475,10 @@
         <v>0</v>
       </c>
       <c r="C1493" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1493" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1493" t="b">
         <v>1</v>
@@ -27497,7 +27497,7 @@
         <v>0</v>
       </c>
       <c r="D1494" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1494" t="b">
         <v>1</v>
@@ -27516,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="D1495" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1495" t="b">
         <v>1</v>
@@ -27535,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="D1496" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1496" t="b">
         <v>1</v>
@@ -27552,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="D1497" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1497" t="b">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="D1498" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1498" t="b">
         <v>0</v>
@@ -27588,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="D1499" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1499" t="b">
         <v>1</v>
@@ -27607,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="D1500" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1500" t="b">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="D1501" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1501" t="b">
         <v>1</v>
@@ -27645,7 +27645,7 @@
         <v>0</v>
       </c>
       <c r="D1502" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27664,7 +27664,7 @@
         <v>0</v>
       </c>
       <c r="D1503" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27683,7 +27683,7 @@
         <v>0</v>
       </c>
       <c r="D1504" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27700,7 +27700,7 @@
         <v>0</v>
       </c>
       <c r="D1505" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27719,7 +27719,7 @@
         <v>0</v>
       </c>
       <c r="D1506" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27738,7 +27738,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1507" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27757,7 +27757,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1508" t="n">
-        <v>-0.6</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27776,7 +27776,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1509" t="n">
-        <v>-0.6</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27795,7 +27795,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1510" t="n">
-        <v>-0.6</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27814,7 +27814,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1511" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27833,7 +27833,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1512" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27852,7 +27852,7 @@
         <v>-1</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27871,7 +27871,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1514" t="b">
         <v>1</v>
@@ -27888,7 +27888,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27907,7 +27907,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -28218,13 +28218,13 @@
         </is>
       </c>
       <c r="B1533" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1533" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28240,10 +28240,10 @@
         <v>0</v>
       </c>
       <c r="C1534" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28259,10 +28259,10 @@
         <v>0</v>
       </c>
       <c r="C1535" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28278,10 +28278,10 @@
         <v>-2</v>
       </c>
       <c r="C1536" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.5</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28297,10 +28297,10 @@
         <v>0</v>
       </c>
       <c r="C1537" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28316,10 +28316,10 @@
         <v>0</v>
       </c>
       <c r="C1538" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28335,10 +28335,10 @@
         <v>-3</v>
       </c>
       <c r="C1539" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28355,7 +28355,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="B1543" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1543" t="n">
-        <v>-1.571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="C1544" t="n">
-        <v>-1.571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28445,10 +28445,10 @@
         <v>2</v>
       </c>
       <c r="C1545" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28462,10 +28462,10 @@
       </c>
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.5</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28481,10 +28481,10 @@
         <v>0</v>
       </c>
       <c r="C1547" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.4</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -28497,13 +28497,13 @@
         </is>
       </c>
       <c r="B1548" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1548" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1548" t="n">
-        <v>-0.3</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1548" t="b">
         <v>1</v>
@@ -28519,10 +28519,10 @@
         <v>-2</v>
       </c>
       <c r="C1549" t="n">
-        <v>0</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1549" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1549" t="b">
         <v>1</v>
@@ -28538,10 +28538,10 @@
         <v>0</v>
       </c>
       <c r="C1550" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1550" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1550" t="b">
         <v>1</v>
@@ -28557,10 +28557,10 @@
         <v>0</v>
       </c>
       <c r="C1551" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1551" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1551" t="b">
         <v>1</v>
@@ -28576,10 +28576,10 @@
         <v>0</v>
       </c>
       <c r="C1552" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1552" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1552" t="b">
         <v>1</v>
@@ -28595,10 +28595,10 @@
         <v>0</v>
       </c>
       <c r="C1553" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1553" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1553" t="b">
         <v>1</v>
@@ -28612,10 +28612,10 @@
       </c>
       <c r="B1554" t="inlineStr"/>
       <c r="C1554" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1554" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1554" t="b">
         <v>0</v>
@@ -28632,7 +28632,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1555" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1555" t="b">
         <v>0</v>
@@ -28649,7 +28649,7 @@
         <v>0</v>
       </c>
       <c r="D1556" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1556" t="b">
         <v>0</v>
@@ -28668,7 +28668,7 @@
         <v>0</v>
       </c>
       <c r="D1557" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1557" t="b">
         <v>1</v>
@@ -28687,9 +28687,28 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1558" t="n">
-        <v>-0.3</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1558" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1559" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1559" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D1559" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="E1559" t="b">
         <v>1</v>
       </c>
     </row>
@@ -28723,7 +28742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-04-09 | Publication days: 917</t>
+          <t>Coverage: 2022-01-04 to 2026-04-10 | Publication days: 918</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1559"/>
+  <dimension ref="A1:E1560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27827,13 +27827,13 @@
         </is>
       </c>
       <c r="B1512" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1512" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D1512" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27849,10 +27849,10 @@
         <v>-2</v>
       </c>
       <c r="C1513" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27868,10 +27868,10 @@
         <v>0</v>
       </c>
       <c r="C1514" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1514" t="b">
         <v>1</v>
@@ -27885,10 +27885,10 @@
       </c>
       <c r="B1515" t="inlineStr"/>
       <c r="C1515" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27904,10 +27904,10 @@
         <v>0</v>
       </c>
       <c r="C1516" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27923,10 +27923,10 @@
         <v>-3</v>
       </c>
       <c r="C1517" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27940,10 +27940,10 @@
       </c>
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27962,7 +27962,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27975,13 +27975,13 @@
         </is>
       </c>
       <c r="B1520" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1520" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -27997,10 +27997,10 @@
         <v>0</v>
       </c>
       <c r="C1521" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28016,10 +28016,10 @@
         <v>0</v>
       </c>
       <c r="C1522" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28035,10 +28035,10 @@
         <v>0</v>
       </c>
       <c r="C1523" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28054,10 +28054,10 @@
         <v>0</v>
       </c>
       <c r="C1524" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28073,10 +28073,10 @@
         <v>3</v>
       </c>
       <c r="C1525" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28092,10 +28092,10 @@
         <v>0</v>
       </c>
       <c r="C1526" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28114,7 +28114,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28133,7 +28133,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28150,7 +28150,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28169,7 +28169,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28188,7 +28188,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28205,7 +28205,7 @@
         <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28224,7 +28224,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28243,7 +28243,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28262,7 +28262,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28281,7 +28281,7 @@
         <v>0</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28300,7 +28300,7 @@
         <v>0</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28319,7 +28319,7 @@
         <v>0</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28338,7 +28338,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28355,7 +28355,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1542" t="b">
         <v>1</v>
@@ -28410,7 +28410,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="E1543" t="b">
         <v>1</v>
@@ -28429,7 +28429,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -28448,7 +28448,7 @@
         <v>-1</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -28465,7 +28465,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1546" t="b">
         <v>0</v>
@@ -28484,7 +28484,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -28497,10 +28497,10 @@
         </is>
       </c>
       <c r="B1548" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1548" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1548" t="n">
         <v>-0.2666666666666667</v>
@@ -28519,7 +28519,7 @@
         <v>-2</v>
       </c>
       <c r="C1549" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1549" t="n">
         <v>-0.2333333333333333</v>
@@ -28538,10 +28538,10 @@
         <v>0</v>
       </c>
       <c r="C1550" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1550" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1550" t="b">
         <v>1</v>
@@ -28557,10 +28557,10 @@
         <v>0</v>
       </c>
       <c r="C1551" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1551" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1551" t="b">
         <v>1</v>
@@ -28576,10 +28576,10 @@
         <v>0</v>
       </c>
       <c r="C1552" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1552" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1552" t="b">
         <v>1</v>
@@ -28595,10 +28595,10 @@
         <v>0</v>
       </c>
       <c r="C1553" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1553" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1553" t="b">
         <v>1</v>
@@ -28612,10 +28612,10 @@
       </c>
       <c r="B1554" t="inlineStr"/>
       <c r="C1554" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1554" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1554" t="b">
         <v>0</v>
@@ -28632,7 +28632,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1555" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1555" t="b">
         <v>0</v>
@@ -28649,7 +28649,7 @@
         <v>0</v>
       </c>
       <c r="D1556" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1556" t="b">
         <v>0</v>
@@ -28668,7 +28668,7 @@
         <v>0</v>
       </c>
       <c r="D1557" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1557" t="b">
         <v>1</v>
@@ -28687,7 +28687,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1558" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1558" t="b">
         <v>1</v>
@@ -28706,9 +28706,28 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1559" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1559" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1560" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D1560" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="E1560" t="b">
         <v>1</v>
       </c>
     </row>
@@ -28742,7 +28761,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-04-10 | Publication days: 918</t>
+          <t>Coverage: 2022-01-04 to 2026-04-11 | Publication days: 919</t>
         </is>
       </c>
     </row>

--- a/data/IT.xlsx
+++ b/data/IT.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1560"/>
+  <dimension ref="A1:E1561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27639,13 +27639,13 @@
         </is>
       </c>
       <c r="B1502" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1502" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1502" t="n">
-        <v>0.1</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1502" t="b">
         <v>1</v>
@@ -27661,10 +27661,10 @@
         <v>0</v>
       </c>
       <c r="C1503" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1503" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27680,10 +27680,10 @@
         <v>0</v>
       </c>
       <c r="C1504" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1504" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27697,10 +27697,10 @@
       </c>
       <c r="B1505" t="inlineStr"/>
       <c r="C1505" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1505" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1505" t="b">
         <v>0</v>
@@ -27716,10 +27716,10 @@
         <v>0</v>
       </c>
       <c r="C1506" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1506" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27735,10 +27735,10 @@
         <v>-3</v>
       </c>
       <c r="C1507" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1507" t="n">
-        <v>0.1</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1507" t="b">
         <v>1</v>
@@ -27754,10 +27754,10 @@
         <v>-2</v>
       </c>
       <c r="C1508" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D1508" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1508" t="b">
         <v>1</v>
@@ -27776,7 +27776,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1509" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1509" t="b">
         <v>1</v>
@@ -27795,7 +27795,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1510" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27814,7 +27814,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1511" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1511" t="b">
         <v>1</v>
@@ -27827,13 +27827,13 @@
         </is>
       </c>
       <c r="B1512" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="C1512" t="n">
-        <v>-1</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1512" t="n">
-        <v>-0.2</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1512" t="b">
         <v>1</v>
@@ -27849,10 +27849,10 @@
         <v>-2</v>
       </c>
       <c r="C1513" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27868,10 +27868,10 @@
         <v>0</v>
       </c>
       <c r="C1514" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1514" t="b">
         <v>1</v>
@@ -27885,10 +27885,10 @@
       </c>
       <c r="B1515" t="inlineStr"/>
       <c r="C1515" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27904,10 +27904,10 @@
         <v>0</v>
       </c>
       <c r="C1516" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27923,10 +27923,10 @@
         <v>-3</v>
       </c>
       <c r="C1517" t="n">
-        <v>-1</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1517" t="b">
         <v>1</v>
@@ -27940,10 +27940,10 @@
       </c>
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="n">
-        <v>-1.428571428571429</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.5</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27962,7 +27962,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.6</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1519" t="b">
         <v>1</v>
@@ -27981,7 +27981,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.7</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -28000,7 +28000,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.7</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -28019,7 +28019,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.7</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -28038,7 +28038,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.7</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1523" t="b">
         <v>1</v>
@@ -28057,7 +28057,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.7</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -28076,7 +28076,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.6</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -28095,7 +28095,7 @@
         <v>0</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.6</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -28114,7 +28114,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.6</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -28133,7 +28133,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.6</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1528" t="b">
         <v>1</v>
@@ -28150,7 +28150,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.6</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -28169,7 +28169,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.6</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -28188,7 +28188,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.6</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -28205,7 +28205,7 @@
         <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.6</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -28224,7 +28224,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -28243,7 +28243,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -28262,7 +28262,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1535" t="b">
         <v>1</v>
@@ -28281,7 +28281,7 @@
         <v>0</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.6</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -28300,7 +28300,7 @@
         <v>0</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.5</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1537" t="b">
         <v>1</v>
@@ -28319,7 +28319,7 @@
         <v>0</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1538" t="b">
         <v>1</v>
@@ -28338,7 +28338,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -28355,7 +28355,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="B1557" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1557" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1557" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1557" t="b">
         <v>1</v>
@@ -28684,10 +28684,10 @@
         <v>2</v>
       </c>
       <c r="C1558" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1558" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1558" t="b">
         <v>1</v>
@@ -28703,10 +28703,10 @@
         <v>0</v>
       </c>
       <c r="C1559" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1559" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1559" t="b">
         <v>1</v>
@@ -28722,13 +28722,30 @@
         <v>0</v>
       </c>
       <c r="C1560" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1560" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1560" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr"/>
+      <c r="C1561" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1561" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="E1561" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -28761,7 +28778,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-04 to 2026-04-11 | Publication days: 919</t>
+          <t>Coverage: 2022-01-04 to 2026-04-12 | Publication days: 919</t>
         </is>
       </c>
     </row>
